--- a/hiring_companies_2026-10-30.xlsx
+++ b/hiring_companies_2026-10-30.xlsx
@@ -477,7 +477,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Disney</t>
+          <t>FXC Intelligence</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,22 +492,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Disney Jobs Remote, Disney Jobs From Home Apply For The Best Job ( Web Designer )</t>
+          <t>Lead Software Engineer (Golang/TypeScript) - Independent Contractor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2478319286364478244</t>
+          <t>https://jooble.org/jdp/2131906267036489636</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Disney</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=FXC+Intelligence</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rula</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,22 +539,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fully Licensed Behavioral Health Therapist (LMFT / LMHC / LICSW)- Remote -Rula - Havre-Saint-Pierre | LPCC Therapist | In-Person | $110-$125/hr | Part-Time - Indian Head | Licensed Marriage and Family</t>
+          <t>Cloud Security Systems Engineer</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6402756346729033148</t>
+          <t>https://jooble.org/jdp/3789459144784592863</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Rula</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Palo+Alto+Networks</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dexcom</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Senior Web Platform Developer</t>
+          <t>Application Security Engineering</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/941802610940688530</t>
+          <t>https://jooble.org/jdp/-5183511788404120859</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Dexcom</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Samsara</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -618,12 +618,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Midwest Veterinary Supply, Inc.</t>
+          <t>Envista Holdings Corporation</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Digital Marketing/Branding Lead</t>
+          <t>Implant Direct- Regional Sales Representative (Indiana) | Regional Sales Representative (Las Vegas, NV)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1889029867799647355</t>
+          <t>https://jooble.org/jdp/-8168238854138706638</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Midwest+Veterinary+Supply%2C+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Envista+Holdings+Corporation</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -665,12 +665,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>United Auto Credit Corporation</t>
+          <t>Aledade PBC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -680,12 +680,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Internal Area Sales Manager</t>
+          <t>Regional Sales Execution Specialist, Remote</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2750322602175314889</t>
+          <t>https://jooble.org/jdp/4933636475130593641</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=United+Auto+Credit+Corporation</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Aledade+PBC</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -712,12 +712,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Calance</t>
+          <t>AOGarcia</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -727,22 +727,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cybersecurity Developer - hybrid (3 days onsite) | Golang Developer - hybrid (3 days onsite)</t>
+          <t>Remote Benefits Sales Representative</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-815760062456587673</t>
+          <t>https://jooble.org/jdp/3294122034589277553</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Calance</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=AOGarcia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -759,12 +759,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Tenna</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Remote : Senior Solution Engineer | Solutions Engineer</t>
+          <t>Sales Engineer (Pacific Coast)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2093569113898995256</t>
+          <t>https://jooble.org/jdp/730915716123042229</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Equifax</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Tenna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -806,12 +806,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ABC Financial Services</t>
+          <t>ITW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -821,12 +821,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VP, Growth Marketing</t>
+          <t>Inside Sales Representative</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2611921100712938673</t>
+          <t>https://jooble.org/jdp/-4847891558427212724</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=ABC+Financial+Services</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ITW</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -853,12 +853,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Stryker</t>
+          <t>American Income Life</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -868,12 +868,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Senior Principal Cloud Developer</t>
+          <t>Remote Sales Representative | Sales Consultant - Remote</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4055084927896021138</t>
+          <t>https://jooble.org/jdp/-6077102703941345168</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Stryker</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=American+Income+Life</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -900,12 +900,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Backbone Media</t>
+          <t>Adtran</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Media Coordinator - Paid Social</t>
+          <t>Sr. Sales Engineer - Telecom</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8509230513007829633</t>
+          <t>https://jooble.org/jdp/-766294332978561640</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Backbone+Media</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Adtran</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -947,12 +947,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Federal Mfg</t>
+          <t>Land O'Lakes</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>REMOTE - Web Marketing Manager</t>
+          <t>Territory Sales Representative</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5243593702999289169</t>
+          <t>https://jooble.org/jdp/-1004670240285544291</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Federal+Mfg</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Land+O%27Lakes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -994,7 +994,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CivicScience</t>
+          <t>Rubicon</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Marketing Intern (Advertising)</t>
+          <t>Outside Sales Executive - Houston, TX</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7057256011969997072</t>
+          <t>https://jooble.org/jdp/1669238501299716404</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CivicScience</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Rubicon</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Infotech</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer (Remote)</t>
+          <t>Sales Representative - Life Sciences (Houston)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6103397366301565668</t>
+          <t>https://jooble.org/jdp/-5561753880944608127</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Infotech</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Avantor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1088,12 +1088,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Zumigo, Inc.</t>
+          <t>472e9ed2-3c84-4920-b620-d4460b4b5473</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1103,22 +1103,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sr Marketing Director</t>
+          <t>Cloud Application Engineer</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/774539563294686030</t>
+          <t>https://jooble.org/jdp/-550395661423155349</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Zumigo%2C+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=472e9ed2-3c84-4920-b620-d4460b4b5473</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1135,12 +1135,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TriMed</t>
+          <t>Mimecast</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Associate Brand Manager</t>
+          <t>Salesforce Account Executive - REMOTE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8325458233777131774</t>
+          <t>https://jooble.org/jdp/5601533015911471334</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=TriMed</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Mimecast</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1182,12 +1182,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HarperCollins Publishers</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Senior Director, Marketing (Bible Gateway) (remote US)</t>
+          <t>Software Engineer, Backend &amp; Distributed Systems (REMOTE)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7335423094189984674</t>
+          <t>https://jooble.org/jdp/7509964094762949469</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=HarperCollins+Publishers</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Home+Depot</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1229,12 +1229,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Mountain Hot Tub</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1244,22 +1244,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sr. Director, Marketing - Retirement &amp; Wealth (Remote) | Sr. Platform Mobile Engineer (Remote)</t>
+          <t>Marketing and Events Director</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1476596549124156944</t>
+          <t>https://jooble.org/jdp/2768380577503981618</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Inspira+Financial</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Mountain+Hot+Tub</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1276,12 +1276,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Core Medical Group</t>
+          <t>StackAdapt</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1291,22 +1291,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Director of Marketing</t>
+          <t>RVP, Client Services - Eastern US</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4954642367004321709</t>
+          <t>https://jooble.org/jdp/8842089623390431537</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Core+Medical+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=StackAdapt</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1323,12 +1323,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lago</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Web Designer</t>
+          <t>Senior Platform Engineer-Cloud</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/5152115638776436139</t>
+          <t>https://jooble.org/jdp/-2176912100933079221</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Lago</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Defense+Unicorns</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1370,7 +1370,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>proGroupX</t>
+          <t>Insulet Corporation</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1385,22 +1385,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Web Designer</t>
+          <t>Territory Sales Specialist (Field Based)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-9182714698129278834</t>
+          <t>https://jooble.org/jdp/6856884819245396484</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=proGroupX</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Insulet+Corporation</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1417,12 +1417,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INTERNATIONAL HIGHLIGHT LLC</t>
+          <t>Basis</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1432,22 +1432,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Web Designer</t>
+          <t>Media Planning Associate</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1351351360015750719</t>
+          <t>https://jooble.org/jdp/-4017247241107932491</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=INTERNATIONAL+HIGHLIGHT+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Basis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1464,12 +1464,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>XYZ Venture Capital</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1479,22 +1479,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Web Designer</t>
+          <t>Lead Cloud Architect | Lead Full Stack Engineer Engineer* | Telecommute Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8988391745723627278</t>
+          <t>https://jooble.org/jdp/518130480741172306</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=XYZ+Venture+Capital</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Humana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kenyan Edu</t>
+          <t>Gcore</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1526,22 +1526,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Web Designer, eCRM</t>
+          <t>DevOps Engineer/SRE (Cloud IaaS)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1737514157874705590</t>
+          <t>https://jooble.org/jdp/2375771576622753792</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kenyan+Edu</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Gcore</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KING ARTHUR FLOUR</t>
+          <t>Search Influence</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1573,22 +1573,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Web Designer</t>
+          <t>Marketing Associate (Digital)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/909933830597200729</t>
+          <t>https://jooble.org/jdp/912158289158436254</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=KING+ARTHUR+FLOUR</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Search+Influence</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1605,12 +1605,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Feedinkoo: Remote Jobs</t>
+          <t>GEHA Health</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1620,22 +1620,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Remote Web Designer for High-Impact Landing Pages</t>
+          <t>Digital Marketing Channel Specialist</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4512808540755280449</t>
+          <t>https://jooble.org/jdp/-8406164082337557941</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Feedinkoo%3A+Remote+Jobs</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=GEHA+Health</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1652,12 +1652,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BABYGOLD</t>
+          <t>SGS Consulting</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1667,22 +1667,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Conversion-Driven Shopify Web Designer Remote Freelance</t>
+          <t>Unit People &amp; Culture Business Partner (Hybrid Role)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6789181394508970777</t>
+          <t>https://jooble.org/jdp/4297982526350696937</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=BABYGOLD</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=SGS+Consulting</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Courier Newsroom</t>
+          <t>Rythm Health</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1714,22 +1714,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Political Correspondent, New Mexico</t>
+          <t>Senior Brand &amp; Web Designer</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-3840761722486792290</t>
+          <t>https://jooble.org/jdp/3821985184231886755</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Courier+Newsroom</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Rythm+Health</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1746,12 +1746,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KTBS - TV</t>
+          <t>InterSources</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1761,22 +1761,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>News Producer</t>
+          <t>Web Designer - Advanced</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2190556388946049571</t>
+          <t>https://jooble.org/jdp/8352802072718370891</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=KTBS+-+TV</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=InterSources</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1793,12 +1793,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Remote Work &amp; Working at Home Jobs</t>
+          <t>Energy Innovation Corp</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1808,22 +1808,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sr. Writer - Creative Agency - Remote</t>
+          <t>Remote-First Web Designer for Microservices &amp; CI/CD | Web Designer</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5422126467539216131</t>
+          <t>https://jooble.org/jdp/4520060461402599743</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Remote+Work+%26+Working+at+Home+Jobs</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Energy+Innovation+Corp</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1840,12 +1840,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Montana-Dakota Utilities Co.</t>
+          <t>Iverson Inc.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1855,22 +1855,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Social Media Manager</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/608198212599097360</t>
+          <t>https://jooble.org/jdp/-418271960183469473</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Montana-Dakota+Utilities+Co.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Iverson+Inc.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1887,12 +1887,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FAT Brands Inc</t>
+          <t>Novovu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1902,22 +1902,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Social Media Manager</t>
+          <t>Frontend Web Designer (Remote)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-3693366917845701822</t>
+          <t>https://jooble.org/jdp/-2298870756951925693</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=FAT+Brands+Inc</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Novovu</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1934,12 +1934,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Rocket Media</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1949,22 +1949,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Social Media Specialist, X</t>
+          <t>Web &amp; Marketing Designer</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-6748494695139980049</t>
+          <t>https://jooble.org/jdp/8563303552087464841</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Nebius</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Rocket+Media</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1981,12 +1981,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Media Works</t>
+          <t>Theoria Creative</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1996,22 +1996,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Media Coordinator</t>
+          <t>Senior Brand &amp; Web Designer — Remote, Part-Time (Biotech)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8086589176379973428</t>
+          <t>https://jooble.org/jdp/6088905054285441446</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Media+Works</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Theoria+Creative</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2028,12 +2028,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kentech</t>
+          <t>Kee Group Marketing</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2043,22 +2043,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VIDEO EDITOR</t>
+          <t>Part-Time Web and Graphic Designer</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/797681984386169026</t>
+          <t>https://jooble.org/jdp/-6763115104913740248</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kentech</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Kee+Group+Marketing</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2075,12 +2075,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Enterprise Monkey</t>
+          <t>Northpeak</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Video Editor</t>
+          <t>Brand and Web Designer (Remote)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7771031896007875901</t>
+          <t>https://jooble.org/jdp/5731986293754680344</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Enterprise+Monkey</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Northpeak</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2122,12 +2122,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jobrapido</t>
+          <t>North American Dental Group</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2137,22 +2137,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Senior Paid Media Manager</t>
+          <t>Conversion-Driven Web &amp; Brand Designer (Remote)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1652974092729948410</t>
+          <t>https://jooble.org/jdp/6020734544837758419</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobrapido</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=North+American+Dental+Group</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2169,12 +2169,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LIGHT OF TRUTH CENTER INC</t>
+          <t>DealerOn, Inc.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2184,22 +2184,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Media Coordinator</t>
+          <t>Remote Junior Web Designer: HTML/CSS &amp; UI</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5262595411542067289</t>
+          <t>https://jooble.org/jdp/-7476411391072883232</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=LIGHT+OF+TRUTH+CENTER+INC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=DealerOn%2C+Inc.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2216,7 +2216,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Agency Support for HighLevel</t>
+          <t>Ezead Media Group.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2231,22 +2231,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Video Editor</t>
+          <t>Web Designer | $65/hr Remote</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-537362122227476282</t>
+          <t>https://jooble.org/jdp/5039967973628153553</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Agency+Support+for+HighLevel</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ezead+Media+Group.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2263,12 +2263,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Social Discovery Group</t>
+          <t>Twine</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2278,22 +2278,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Product Marketing Manager</t>
+          <t>Web Designer - Remote</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1490479571422966160</t>
+          <t>https://jooble.org/jdp/5009281842371498704</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Social+Discovery+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Twine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2310,12 +2310,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>MAG - MyAmazon Guy.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2325,22 +2325,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Senior Creative Strategist, Performance Marketing</t>
+          <t>Head of Performance Marketing | UI/UX Web Designer</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6882429796946625621</t>
+          <t>https://jooble.org/jdp/-493421990620413090</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Block</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=MAG+-+MyAmazon+Guy.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2357,12 +2357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SuperOrdinaryCo, Inc.</t>
+          <t>Rank Rise Marketing</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2372,22 +2372,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Chief Marketing Officer (CMO)</t>
+          <t>Senior Web Designer</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7636804770551256815</t>
+          <t>https://jooble.org/jdp/-642218675040554302</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=SuperOrdinaryCo%2C+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Rank+Rise+Marketing</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2404,12 +2404,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ivy Fertility Services, LLC</t>
+          <t>Greystar</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2419,22 +2419,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Chief Marketing Officer</t>
+          <t>Senior Web Experience Designer - Remote UX Lead</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1241299352397776468</t>
+          <t>https://jooble.org/jdp/5928767549313958511</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Ivy+Fertility+Services%2C+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Greystar</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2451,12 +2451,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Wynne Systems</t>
+          <t>THE/STUDIO</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2466,22 +2466,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Product Marketing Specialist</t>
+          <t>Video Editor - Social, Paid Ads &amp; YouTube</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-47683280982768467</t>
+          <t>https://jooble.org/jdp/6645165160458322383</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Wynne+Systems</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=THE%2FSTUDIO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2498,12 +2498,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Economic Media</t>
+          <t>Express Chipping Inc</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2513,22 +2513,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Growth Marketing Associate (Remote)</t>
+          <t>Social Media &amp; Reputation Specialist</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8195186423080429722</t>
+          <t>https://jooble.org/jdp/-8517405573874683921</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Economic+Media</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Express+Chipping+Inc</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2545,12 +2545,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Appspace</t>
+          <t>Jobs for Humanity</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2560,22 +2560,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Digital Marketing Manager - Americas</t>
+          <t>Marketing Director - Full Remote</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2086120899100106215</t>
+          <t>https://jooble.org/jdp/1858879860399921083</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Appspace</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobs+for+Humanity</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2592,12 +2592,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Cielo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2607,22 +2607,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Marketing Manager Sr</t>
+          <t>Specialist - Marketing Operations</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1089199718114661826</t>
+          <t>https://jooble.org/jdp/8940518011192555958</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Amcor</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Cielo</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2639,12 +2639,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Black Rifle Coffee Company</t>
+          <t>Wm Bolthouse Farms Inc</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2654,22 +2654,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Skillbridge Extern - Marketing</t>
+          <t>Influencer Marketing Coordinator</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7251647884982290193</t>
+          <t>https://jooble.org/jdp/-4206387976728994704</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Black+Rifle+Coffee+Company</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Wm+Bolthouse+Farms+Inc</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2686,7 +2686,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KangarooHealth Inc.</t>
+          <t>Finance of America</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2701,22 +2701,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Senior Marketing Manager</t>
+          <t>Brand Director</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4203111684881695745</t>
+          <t>https://jooble.org/jdp/6261290980586395894</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=KangarooHealth+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Finance+of+America</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Homefront Brands</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2748,22 +2748,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Batch Application Programmer (C, UNIX/Linux) | Batch Application Programmer (C,C++, UNIX/Linux) | C# .NET Developer | NCPCP - UI Developer | Senior Full Stack Application Developer (.NET) | Senior Pro</t>
+          <t>Franchise Brand Marketing Manager</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5236239325341792582</t>
+          <t>https://jooble.org/jdp/-6768127774903740187</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Gainwell+Technologies+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Homefront+Brands</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2780,12 +2780,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BAM Technologies, LLC</t>
+          <t>VSS Digital</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2795,22 +2795,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Digital Marketing Executive</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/981567298801070419</t>
+          <t>https://jooble.org/jdp/-5288324093223393445</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=BAM+Technologies%2C+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=VSS+Digital</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
